--- a/files/temp_files/statement_2026_02.xlsx
+++ b/files/temp_files/statement_2026_02.xlsx
@@ -588,7 +588,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>61.19</v>
+        <v>-61.19</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -602,7 +602,7 @@
         <v>33</v>
       </c>
       <c r="C3">
-        <v>239.96</v>
+        <v>-239.96</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -616,7 +616,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>48.18</v>
+        <v>-48.18</v>
       </c>
       <c r="D4" t="s">
         <v>58</v>
@@ -644,7 +644,7 @@
         <v>36</v>
       </c>
       <c r="C6">
-        <v>4.45</v>
+        <v>-4.45</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -658,7 +658,7 @@
         <v>37</v>
       </c>
       <c r="C7">
-        <v>314.78</v>
+        <v>-314.78</v>
       </c>
       <c r="D7" t="s">
         <v>61</v>
@@ -672,7 +672,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>19.82</v>
+        <v>-19.82</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -700,7 +700,7 @@
         <v>37</v>
       </c>
       <c r="C10">
-        <v>976.75</v>
+        <v>-976.75</v>
       </c>
       <c r="D10" t="s">
         <v>61</v>
@@ -714,7 +714,7 @@
         <v>38</v>
       </c>
       <c r="C11">
-        <v>144.18</v>
+        <v>-144.18</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>
@@ -728,7 +728,7 @@
         <v>39</v>
       </c>
       <c r="C12">
-        <v>52.98</v>
+        <v>-52.98</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -742,7 +742,7 @@
         <v>40</v>
       </c>
       <c r="C13">
-        <v>88.48999999999999</v>
+        <v>-88.48999999999999</v>
       </c>
       <c r="D13" t="s">
         <v>62</v>
@@ -756,7 +756,7 @@
         <v>41</v>
       </c>
       <c r="C14">
-        <v>379.54</v>
+        <v>-379.54</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -770,7 +770,7 @@
         <v>42</v>
       </c>
       <c r="C15">
-        <v>274.7</v>
+        <v>-274.7</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -784,7 +784,7 @@
         <v>43</v>
       </c>
       <c r="C16">
-        <v>130.41</v>
+        <v>-130.41</v>
       </c>
       <c r="D16" t="s">
         <v>58</v>
@@ -798,7 +798,7 @@
         <v>37</v>
       </c>
       <c r="C17">
-        <v>12.74</v>
+        <v>-12.74</v>
       </c>
       <c r="D17" t="s">
         <v>61</v>
@@ -812,7 +812,7 @@
         <v>43</v>
       </c>
       <c r="C18">
-        <v>150.69</v>
+        <v>-150.69</v>
       </c>
       <c r="D18" t="s">
         <v>58</v>
@@ -826,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="C19">
-        <v>134.66</v>
+        <v>-134.66</v>
       </c>
       <c r="D19" t="s">
         <v>58</v>
@@ -840,7 +840,7 @@
         <v>41</v>
       </c>
       <c r="C20">
-        <v>766.26</v>
+        <v>-766.26</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
@@ -854,7 +854,7 @@
         <v>44</v>
       </c>
       <c r="C21">
-        <v>252.68</v>
+        <v>-252.68</v>
       </c>
       <c r="D21" t="s">
         <v>57</v>
@@ -868,7 +868,7 @@
         <v>34</v>
       </c>
       <c r="C22">
-        <v>145.28</v>
+        <v>-145.28</v>
       </c>
       <c r="D22" t="s">
         <v>58</v>
@@ -882,7 +882,7 @@
         <v>45</v>
       </c>
       <c r="C23">
-        <v>35.8</v>
+        <v>-35.8</v>
       </c>
       <c r="D23" t="s">
         <v>56</v>
@@ -896,7 +896,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>955.92</v>
+        <v>-955.92</v>
       </c>
       <c r="D24" t="s">
         <v>61</v>
@@ -910,7 +910,7 @@
         <v>46</v>
       </c>
       <c r="C25">
-        <v>88.89</v>
+        <v>-88.89</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
@@ -924,7 +924,7 @@
         <v>47</v>
       </c>
       <c r="C26">
-        <v>3.69</v>
+        <v>-3.69</v>
       </c>
       <c r="D26" t="s">
         <v>60</v>
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="C27">
-        <v>498.67</v>
+        <v>-498.67</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="C28">
-        <v>82.73</v>
+        <v>-82.73</v>
       </c>
       <c r="D28" t="s">
         <v>62</v>
@@ -966,7 +966,7 @@
         <v>48</v>
       </c>
       <c r="C29">
-        <v>299.98</v>
+        <v>-299.98</v>
       </c>
       <c r="D29" t="s">
         <v>63</v>
@@ -994,7 +994,7 @@
         <v>51</v>
       </c>
       <c r="C31">
-        <v>255.08</v>
+        <v>-255.08</v>
       </c>
       <c r="D31" t="s">
         <v>63</v>
@@ -1008,7 +1008,7 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>210.79</v>
+        <v>-210.79</v>
       </c>
       <c r="D32" t="s">
         <v>61</v>
@@ -1036,7 +1036,7 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>248.12</v>
+        <v>-248.12</v>
       </c>
       <c r="D34" t="s">
         <v>57</v>
@@ -1050,7 +1050,7 @@
         <v>37</v>
       </c>
       <c r="C35">
-        <v>159.84</v>
+        <v>-159.84</v>
       </c>
       <c r="D35" t="s">
         <v>61</v>
@@ -1064,7 +1064,7 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>854.0700000000001</v>
+        <v>-854.0700000000001</v>
       </c>
       <c r="D36" t="s">
         <v>61</v>
@@ -1078,7 +1078,7 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>7.91</v>
+        <v>-7.91</v>
       </c>
       <c r="D37" t="s">
         <v>60</v>
@@ -1092,7 +1092,7 @@
         <v>42</v>
       </c>
       <c r="C38">
-        <v>363.73</v>
+        <v>-363.73</v>
       </c>
       <c r="D38" t="s">
         <v>61</v>
@@ -1106,7 +1106,7 @@
         <v>52</v>
       </c>
       <c r="C39">
-        <v>435.26</v>
+        <v>-435.26</v>
       </c>
       <c r="D39" t="s">
         <v>63</v>
@@ -1120,7 +1120,7 @@
         <v>34</v>
       </c>
       <c r="C40">
-        <v>48.71</v>
+        <v>-48.71</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
@@ -1148,7 +1148,7 @@
         <v>44</v>
       </c>
       <c r="C42">
-        <v>74.63</v>
+        <v>-74.63</v>
       </c>
       <c r="D42" t="s">
         <v>57</v>
@@ -1162,7 +1162,7 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>378.94</v>
+        <v>-378.94</v>
       </c>
       <c r="D43" t="s">
         <v>61</v>
@@ -1190,7 +1190,7 @@
         <v>48</v>
       </c>
       <c r="C45">
-        <v>260.17</v>
+        <v>-260.17</v>
       </c>
       <c r="D45" t="s">
         <v>63</v>
@@ -1204,7 +1204,7 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>75.78</v>
+        <v>-75.78</v>
       </c>
       <c r="D46" t="s">
         <v>58</v>
@@ -1218,7 +1218,7 @@
         <v>40</v>
       </c>
       <c r="C47">
-        <v>139.41</v>
+        <v>-139.41</v>
       </c>
       <c r="D47" t="s">
         <v>62</v>
@@ -1232,7 +1232,7 @@
         <v>44</v>
       </c>
       <c r="C48">
-        <v>185.45</v>
+        <v>-185.45</v>
       </c>
       <c r="D48" t="s">
         <v>57</v>
@@ -1274,7 +1274,7 @@
         <v>43</v>
       </c>
       <c r="C51">
-        <v>62.28</v>
+        <v>-62.28</v>
       </c>
       <c r="D51" t="s">
         <v>58</v>
@@ -1288,7 +1288,7 @@
         <v>32</v>
       </c>
       <c r="C52">
-        <v>44.66</v>
+        <v>-44.66</v>
       </c>
       <c r="D52" t="s">
         <v>56</v>
@@ -1302,7 +1302,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>134.33</v>
+        <v>-134.33</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
@@ -1316,7 +1316,7 @@
         <v>52</v>
       </c>
       <c r="C54">
-        <v>10.9</v>
+        <v>-10.9</v>
       </c>
       <c r="D54" t="s">
         <v>63</v>
@@ -1330,7 +1330,7 @@
         <v>55</v>
       </c>
       <c r="C55">
-        <v>32.42</v>
+        <v>-32.42</v>
       </c>
       <c r="D55" t="s">
         <v>60</v>
@@ -1344,7 +1344,7 @@
         <v>46</v>
       </c>
       <c r="C56">
-        <v>82</v>
+        <v>-82</v>
       </c>
       <c r="D56" t="s">
         <v>56</v>
@@ -1358,7 +1358,7 @@
         <v>55</v>
       </c>
       <c r="C57">
-        <v>16.33</v>
+        <v>-16.33</v>
       </c>
       <c r="D57" t="s">
         <v>60</v>
@@ -1372,7 +1372,7 @@
         <v>44</v>
       </c>
       <c r="C58">
-        <v>261.84</v>
+        <v>-261.84</v>
       </c>
       <c r="D58" t="s">
         <v>57</v>
@@ -1386,7 +1386,7 @@
         <v>52</v>
       </c>
       <c r="C59">
-        <v>305.91</v>
+        <v>-305.91</v>
       </c>
       <c r="D59" t="s">
         <v>63</v>
@@ -1400,7 +1400,7 @@
         <v>34</v>
       </c>
       <c r="C60">
-        <v>51.04</v>
+        <v>-51.04</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
@@ -1414,7 +1414,7 @@
         <v>48</v>
       </c>
       <c r="C61">
-        <v>441.21</v>
+        <v>-441.21</v>
       </c>
       <c r="D61" t="s">
         <v>63</v>
@@ -1428,7 +1428,7 @@
         <v>49</v>
       </c>
       <c r="C62">
-        <v>80.93000000000001</v>
+        <v>-80.93000000000001</v>
       </c>
       <c r="D62" t="s">
         <v>62</v>
@@ -1442,7 +1442,7 @@
         <v>37</v>
       </c>
       <c r="C63">
-        <v>490.23</v>
+        <v>-490.23</v>
       </c>
       <c r="D63" t="s">
         <v>61</v>
@@ -1470,7 +1470,7 @@
         <v>46</v>
       </c>
       <c r="C65">
-        <v>81.02</v>
+        <v>-81.02</v>
       </c>
       <c r="D65" t="s">
         <v>56</v>
@@ -1484,7 +1484,7 @@
         <v>43</v>
       </c>
       <c r="C66">
-        <v>78.14</v>
+        <v>-78.14</v>
       </c>
       <c r="D66" t="s">
         <v>58</v>
@@ -1498,7 +1498,7 @@
         <v>47</v>
       </c>
       <c r="C67">
-        <v>30.55</v>
+        <v>-30.55</v>
       </c>
       <c r="D67" t="s">
         <v>60</v>
@@ -1512,7 +1512,7 @@
         <v>45</v>
       </c>
       <c r="C68">
-        <v>52.84</v>
+        <v>-52.84</v>
       </c>
       <c r="D68" t="s">
         <v>56</v>
@@ -1526,7 +1526,7 @@
         <v>54</v>
       </c>
       <c r="C69">
-        <v>37.14</v>
+        <v>-37.14</v>
       </c>
       <c r="D69" t="s">
         <v>58</v>
@@ -1540,7 +1540,7 @@
         <v>49</v>
       </c>
       <c r="C70">
-        <v>147.97</v>
+        <v>-147.97</v>
       </c>
       <c r="D70" t="s">
         <v>62</v>
@@ -1554,7 +1554,7 @@
         <v>48</v>
       </c>
       <c r="C71">
-        <v>447.23</v>
+        <v>-447.23</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -1568,7 +1568,7 @@
         <v>43</v>
       </c>
       <c r="C72">
-        <v>98.34999999999999</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="D72" t="s">
         <v>58</v>
@@ -1582,7 +1582,7 @@
         <v>34</v>
       </c>
       <c r="C73">
-        <v>87.29000000000001</v>
+        <v>-87.29000000000001</v>
       </c>
       <c r="D73" t="s">
         <v>58</v>
@@ -1610,7 +1610,7 @@
         <v>55</v>
       </c>
       <c r="C75">
-        <v>22.51</v>
+        <v>-22.51</v>
       </c>
       <c r="D75" t="s">
         <v>60</v>
@@ -1624,7 +1624,7 @@
         <v>51</v>
       </c>
       <c r="C76">
-        <v>295.74</v>
+        <v>-295.74</v>
       </c>
       <c r="D76" t="s">
         <v>63</v>
@@ -1652,7 +1652,7 @@
         <v>54</v>
       </c>
       <c r="C78">
-        <v>150.41</v>
+        <v>-150.41</v>
       </c>
       <c r="D78" t="s">
         <v>58</v>
@@ -1666,7 +1666,7 @@
         <v>48</v>
       </c>
       <c r="C79">
-        <v>323.08</v>
+        <v>-323.08</v>
       </c>
       <c r="D79" t="s">
         <v>63</v>
@@ -1680,7 +1680,7 @@
         <v>47</v>
       </c>
       <c r="C80">
-        <v>40.47</v>
+        <v>-40.47</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
@@ -1694,7 +1694,7 @@
         <v>33</v>
       </c>
       <c r="C81">
-        <v>37.17</v>
+        <v>-37.17</v>
       </c>
       <c r="D81" t="s">
         <v>57</v>
@@ -1708,7 +1708,7 @@
         <v>49</v>
       </c>
       <c r="C82">
-        <v>64.18000000000001</v>
+        <v>-64.18000000000001</v>
       </c>
       <c r="D82" t="s">
         <v>62</v>
@@ -1722,7 +1722,7 @@
         <v>41</v>
       </c>
       <c r="C83">
-        <v>860.75</v>
+        <v>-860.75</v>
       </c>
       <c r="D83" t="s">
         <v>61</v>
@@ -1736,7 +1736,7 @@
         <v>43</v>
       </c>
       <c r="C84">
-        <v>186.3</v>
+        <v>-186.3</v>
       </c>
       <c r="D84" t="s">
         <v>58</v>
@@ -1750,7 +1750,7 @@
         <v>52</v>
       </c>
       <c r="C85">
-        <v>470.59</v>
+        <v>-470.59</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -1764,7 +1764,7 @@
         <v>44</v>
       </c>
       <c r="C86">
-        <v>90.64</v>
+        <v>-90.64</v>
       </c>
       <c r="D86" t="s">
         <v>57</v>
@@ -1792,7 +1792,7 @@
         <v>41</v>
       </c>
       <c r="C88">
-        <v>40.29</v>
+        <v>-40.29</v>
       </c>
       <c r="D88" t="s">
         <v>61</v>
@@ -1806,7 +1806,7 @@
         <v>51</v>
       </c>
       <c r="C89">
-        <v>265.93</v>
+        <v>-265.93</v>
       </c>
       <c r="D89" t="s">
         <v>63</v>
@@ -1820,7 +1820,7 @@
         <v>40</v>
       </c>
       <c r="C90">
-        <v>37.22</v>
+        <v>-37.22</v>
       </c>
       <c r="D90" t="s">
         <v>62</v>
@@ -1834,7 +1834,7 @@
         <v>55</v>
       </c>
       <c r="C91">
-        <v>15.89</v>
+        <v>-15.89</v>
       </c>
       <c r="D91" t="s">
         <v>60</v>
@@ -1848,7 +1848,7 @@
         <v>47</v>
       </c>
       <c r="C92">
-        <v>21.73</v>
+        <v>-21.73</v>
       </c>
       <c r="D92" t="s">
         <v>60</v>
@@ -1862,7 +1862,7 @@
         <v>36</v>
       </c>
       <c r="C93">
-        <v>17.07</v>
+        <v>-17.07</v>
       </c>
       <c r="D93" t="s">
         <v>60</v>
@@ -1876,7 +1876,7 @@
         <v>39</v>
       </c>
       <c r="C94">
-        <v>48.62</v>
+        <v>-48.62</v>
       </c>
       <c r="D94" t="s">
         <v>57</v>
@@ -1890,7 +1890,7 @@
         <v>40</v>
       </c>
       <c r="C95">
-        <v>84.31999999999999</v>
+        <v>-84.31999999999999</v>
       </c>
       <c r="D95" t="s">
         <v>62</v>
@@ -1904,7 +1904,7 @@
         <v>40</v>
       </c>
       <c r="C96">
-        <v>85.81</v>
+        <v>-85.81</v>
       </c>
       <c r="D96" t="s">
         <v>62</v>
@@ -1918,7 +1918,7 @@
         <v>48</v>
       </c>
       <c r="C97">
-        <v>180.23</v>
+        <v>-180.23</v>
       </c>
       <c r="D97" t="s">
         <v>63</v>
@@ -1932,7 +1932,7 @@
         <v>33</v>
       </c>
       <c r="C98">
-        <v>236.86</v>
+        <v>-236.86</v>
       </c>
       <c r="D98" t="s">
         <v>57</v>
@@ -1946,7 +1946,7 @@
         <v>52</v>
       </c>
       <c r="C99">
-        <v>449.99</v>
+        <v>-449.99</v>
       </c>
       <c r="D99" t="s">
         <v>63</v>
@@ -1960,7 +1960,7 @@
         <v>32</v>
       </c>
       <c r="C100">
-        <v>25.25</v>
+        <v>-25.25</v>
       </c>
       <c r="D100" t="s">
         <v>56</v>
@@ -1974,7 +1974,7 @@
         <v>52</v>
       </c>
       <c r="C101">
-        <v>251.59</v>
+        <v>-251.59</v>
       </c>
       <c r="D101" t="s">
         <v>63</v>
@@ -1988,7 +1988,7 @@
         <v>47</v>
       </c>
       <c r="C102">
-        <v>7.89</v>
+        <v>-7.89</v>
       </c>
       <c r="D102" t="s">
         <v>60</v>
@@ -2002,7 +2002,7 @@
         <v>48</v>
       </c>
       <c r="C103">
-        <v>488.4</v>
+        <v>-488.4</v>
       </c>
       <c r="D103" t="s">
         <v>63</v>
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="C104">
-        <v>33.03</v>
+        <v>-33.03</v>
       </c>
       <c r="D104" t="s">
         <v>60</v>
@@ -2030,7 +2030,7 @@
         <v>52</v>
       </c>
       <c r="C105">
-        <v>317.23</v>
+        <v>-317.23</v>
       </c>
       <c r="D105" t="s">
         <v>63</v>
@@ -2044,7 +2044,7 @@
         <v>33</v>
       </c>
       <c r="C106">
-        <v>87.02</v>
+        <v>-87.02</v>
       </c>
       <c r="D106" t="s">
         <v>57</v>
@@ -2072,7 +2072,7 @@
         <v>32</v>
       </c>
       <c r="C108">
-        <v>36.24</v>
+        <v>-36.24</v>
       </c>
       <c r="D108" t="s">
         <v>56</v>
@@ -2086,7 +2086,7 @@
         <v>55</v>
       </c>
       <c r="C109">
-        <v>34.45</v>
+        <v>-34.45</v>
       </c>
       <c r="D109" t="s">
         <v>60</v>
@@ -2100,7 +2100,7 @@
         <v>44</v>
       </c>
       <c r="C110">
-        <v>163.6</v>
+        <v>-163.6</v>
       </c>
       <c r="D110" t="s">
         <v>57</v>
@@ -2114,7 +2114,7 @@
         <v>54</v>
       </c>
       <c r="C111">
-        <v>80.09999999999999</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="D111" t="s">
         <v>58</v>
@@ -2128,7 +2128,7 @@
         <v>33</v>
       </c>
       <c r="C112">
-        <v>282.98</v>
+        <v>-282.98</v>
       </c>
       <c r="D112" t="s">
         <v>57</v>
@@ -2142,7 +2142,7 @@
         <v>38</v>
       </c>
       <c r="C113">
-        <v>85.66</v>
+        <v>-85.66</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2156,7 +2156,7 @@
         <v>55</v>
       </c>
       <c r="C114">
-        <v>42.32</v>
+        <v>-42.32</v>
       </c>
       <c r="D114" t="s">
         <v>60</v>
@@ -2170,7 +2170,7 @@
         <v>34</v>
       </c>
       <c r="C115">
-        <v>57.88</v>
+        <v>-57.88</v>
       </c>
       <c r="D115" t="s">
         <v>58</v>
@@ -2184,7 +2184,7 @@
         <v>52</v>
       </c>
       <c r="C116">
-        <v>496.69</v>
+        <v>-496.69</v>
       </c>
       <c r="D116" t="s">
         <v>63</v>
@@ -2212,7 +2212,7 @@
         <v>44</v>
       </c>
       <c r="C118">
-        <v>172.42</v>
+        <v>-172.42</v>
       </c>
       <c r="D118" t="s">
         <v>57</v>
@@ -2226,7 +2226,7 @@
         <v>38</v>
       </c>
       <c r="C119">
-        <v>62.62</v>
+        <v>-62.62</v>
       </c>
       <c r="D119" t="s">
         <v>62</v>
@@ -2240,7 +2240,7 @@
         <v>49</v>
       </c>
       <c r="C120">
-        <v>74.39</v>
+        <v>-74.39</v>
       </c>
       <c r="D120" t="s">
         <v>62</v>
@@ -2254,7 +2254,7 @@
         <v>46</v>
       </c>
       <c r="C121">
-        <v>50.35</v>
+        <v>-50.35</v>
       </c>
       <c r="D121" t="s">
         <v>56</v>
@@ -2268,7 +2268,7 @@
         <v>49</v>
       </c>
       <c r="C122">
-        <v>74.83</v>
+        <v>-74.83</v>
       </c>
       <c r="D122" t="s">
         <v>62</v>
@@ -2282,7 +2282,7 @@
         <v>38</v>
       </c>
       <c r="C123">
-        <v>118.07</v>
+        <v>-118.07</v>
       </c>
       <c r="D123" t="s">
         <v>62</v>
@@ -2296,7 +2296,7 @@
         <v>39</v>
       </c>
       <c r="C124">
-        <v>156.86</v>
+        <v>-156.86</v>
       </c>
       <c r="D124" t="s">
         <v>57</v>
@@ -2310,7 +2310,7 @@
         <v>52</v>
       </c>
       <c r="C125">
-        <v>65.53</v>
+        <v>-65.53</v>
       </c>
       <c r="D125" t="s">
         <v>63</v>
@@ -2338,7 +2338,7 @@
         <v>45</v>
       </c>
       <c r="C127">
-        <v>81.16</v>
+        <v>-81.16</v>
       </c>
       <c r="D127" t="s">
         <v>56</v>
@@ -2352,7 +2352,7 @@
         <v>51</v>
       </c>
       <c r="C128">
-        <v>423.53</v>
+        <v>-423.53</v>
       </c>
       <c r="D128" t="s">
         <v>63</v>
@@ -2366,7 +2366,7 @@
         <v>32</v>
       </c>
       <c r="C129">
-        <v>73.18000000000001</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="D129" t="s">
         <v>56</v>
@@ -2394,7 +2394,7 @@
         <v>36</v>
       </c>
       <c r="C131">
-        <v>38.56</v>
+        <v>-38.56</v>
       </c>
       <c r="D131" t="s">
         <v>60</v>
@@ -2408,7 +2408,7 @@
         <v>48</v>
       </c>
       <c r="C132">
-        <v>32.6</v>
+        <v>-32.6</v>
       </c>
       <c r="D132" t="s">
         <v>63</v>
@@ -2422,7 +2422,7 @@
         <v>47</v>
       </c>
       <c r="C133">
-        <v>2.57</v>
+        <v>-2.57</v>
       </c>
       <c r="D133" t="s">
         <v>60</v>
@@ -2436,7 +2436,7 @@
         <v>36</v>
       </c>
       <c r="C134">
-        <v>18.68</v>
+        <v>-18.68</v>
       </c>
       <c r="D134" t="s">
         <v>60</v>
@@ -2450,7 +2450,7 @@
         <v>38</v>
       </c>
       <c r="C135">
-        <v>53.5</v>
+        <v>-53.5</v>
       </c>
       <c r="D135" t="s">
         <v>62</v>
@@ -2464,7 +2464,7 @@
         <v>33</v>
       </c>
       <c r="C136">
-        <v>225.44</v>
+        <v>-225.44</v>
       </c>
       <c r="D136" t="s">
         <v>57</v>
@@ -2478,7 +2478,7 @@
         <v>36</v>
       </c>
       <c r="C137">
-        <v>11.59</v>
+        <v>-11.59</v>
       </c>
       <c r="D137" t="s">
         <v>60</v>
@@ -2492,7 +2492,7 @@
         <v>34</v>
       </c>
       <c r="C138">
-        <v>95.3</v>
+        <v>-95.3</v>
       </c>
       <c r="D138" t="s">
         <v>58</v>
@@ -2506,7 +2506,7 @@
         <v>42</v>
       </c>
       <c r="C139">
-        <v>242.1</v>
+        <v>-242.1</v>
       </c>
       <c r="D139" t="s">
         <v>61</v>
@@ -2520,7 +2520,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>158.67</v>
+        <v>-158.67</v>
       </c>
       <c r="D140" t="s">
         <v>57</v>
@@ -2534,7 +2534,7 @@
         <v>45</v>
       </c>
       <c r="C141">
-        <v>42.49</v>
+        <v>-42.49</v>
       </c>
       <c r="D141" t="s">
         <v>56</v>
@@ -2548,7 +2548,7 @@
         <v>39</v>
       </c>
       <c r="C142">
-        <v>50.39</v>
+        <v>-50.39</v>
       </c>
       <c r="D142" t="s">
         <v>57</v>
@@ -2562,7 +2562,7 @@
         <v>40</v>
       </c>
       <c r="C143">
-        <v>24.62</v>
+        <v>-24.62</v>
       </c>
       <c r="D143" t="s">
         <v>62</v>
@@ -2576,7 +2576,7 @@
         <v>45</v>
       </c>
       <c r="C144">
-        <v>52.5</v>
+        <v>-52.5</v>
       </c>
       <c r="D144" t="s">
         <v>56</v>
@@ -2590,7 +2590,7 @@
         <v>48</v>
       </c>
       <c r="C145">
-        <v>326.44</v>
+        <v>-326.44</v>
       </c>
       <c r="D145" t="s">
         <v>63</v>
@@ -2604,7 +2604,7 @@
         <v>47</v>
       </c>
       <c r="C146">
-        <v>9.800000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D146" t="s">
         <v>60</v>
@@ -2618,7 +2618,7 @@
         <v>54</v>
       </c>
       <c r="C147">
-        <v>176.67</v>
+        <v>-176.67</v>
       </c>
       <c r="D147" t="s">
         <v>58</v>
@@ -2632,7 +2632,7 @@
         <v>41</v>
       </c>
       <c r="C148">
-        <v>96.87</v>
+        <v>-96.87</v>
       </c>
       <c r="D148" t="s">
         <v>61</v>
@@ -2660,7 +2660,7 @@
         <v>38</v>
       </c>
       <c r="C150">
-        <v>110.69</v>
+        <v>-110.69</v>
       </c>
       <c r="D150" t="s">
         <v>62</v>
@@ -2688,7 +2688,7 @@
         <v>44</v>
       </c>
       <c r="C152">
-        <v>145.24</v>
+        <v>-145.24</v>
       </c>
       <c r="D152" t="s">
         <v>57</v>
@@ -2702,7 +2702,7 @@
         <v>54</v>
       </c>
       <c r="C153">
-        <v>149.39</v>
+        <v>-149.39</v>
       </c>
       <c r="D153" t="s">
         <v>58</v>
@@ -2716,7 +2716,7 @@
         <v>46</v>
       </c>
       <c r="C154">
-        <v>37.66</v>
+        <v>-37.66</v>
       </c>
       <c r="D154" t="s">
         <v>56</v>
@@ -2730,7 +2730,7 @@
         <v>52</v>
       </c>
       <c r="C155">
-        <v>161.23</v>
+        <v>-161.23</v>
       </c>
       <c r="D155" t="s">
         <v>63</v>
@@ -2744,7 +2744,7 @@
         <v>48</v>
       </c>
       <c r="C156">
-        <v>249.32</v>
+        <v>-249.32</v>
       </c>
       <c r="D156" t="s">
         <v>63</v>
@@ -2758,7 +2758,7 @@
         <v>41</v>
       </c>
       <c r="C157">
-        <v>446.94</v>
+        <v>-446.94</v>
       </c>
       <c r="D157" t="s">
         <v>61</v>
@@ -2772,7 +2772,7 @@
         <v>51</v>
       </c>
       <c r="C158">
-        <v>30.85</v>
+        <v>-30.85</v>
       </c>
       <c r="D158" t="s">
         <v>63</v>
@@ -2786,7 +2786,7 @@
         <v>32</v>
       </c>
       <c r="C159">
-        <v>55.4</v>
+        <v>-55.4</v>
       </c>
       <c r="D159" t="s">
         <v>56</v>
@@ -2800,7 +2800,7 @@
         <v>33</v>
       </c>
       <c r="C160">
-        <v>38.47</v>
+        <v>-38.47</v>
       </c>
       <c r="D160" t="s">
         <v>57</v>
@@ -2814,7 +2814,7 @@
         <v>33</v>
       </c>
       <c r="C161">
-        <v>121.78</v>
+        <v>-121.78</v>
       </c>
       <c r="D161" t="s">
         <v>57</v>
@@ -2828,7 +2828,7 @@
         <v>38</v>
       </c>
       <c r="C162">
-        <v>28.59</v>
+        <v>-28.59</v>
       </c>
       <c r="D162" t="s">
         <v>62</v>
@@ -2842,7 +2842,7 @@
         <v>36</v>
       </c>
       <c r="C163">
-        <v>21.95</v>
+        <v>-21.95</v>
       </c>
       <c r="D163" t="s">
         <v>60</v>
@@ -2870,7 +2870,7 @@
         <v>47</v>
       </c>
       <c r="C165">
-        <v>47.03</v>
+        <v>-47.03</v>
       </c>
       <c r="D165" t="s">
         <v>60</v>
@@ -2884,7 +2884,7 @@
         <v>46</v>
       </c>
       <c r="C166">
-        <v>52.29</v>
+        <v>-52.29</v>
       </c>
       <c r="D166" t="s">
         <v>56</v>
@@ -2898,7 +2898,7 @@
         <v>46</v>
       </c>
       <c r="C167">
-        <v>12.66</v>
+        <v>-12.66</v>
       </c>
       <c r="D167" t="s">
         <v>56</v>
@@ -2912,7 +2912,7 @@
         <v>34</v>
       </c>
       <c r="C168">
-        <v>163.61</v>
+        <v>-163.61</v>
       </c>
       <c r="D168" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>45</v>
       </c>
       <c r="C169">
-        <v>37.44</v>
+        <v>-37.44</v>
       </c>
       <c r="D169" t="s">
         <v>56</v>
@@ -2940,7 +2940,7 @@
         <v>42</v>
       </c>
       <c r="C170">
-        <v>595.08</v>
+        <v>-595.08</v>
       </c>
       <c r="D170" t="s">
         <v>61</v>
@@ -2968,7 +2968,7 @@
         <v>51</v>
       </c>
       <c r="C172">
-        <v>423.69</v>
+        <v>-423.69</v>
       </c>
       <c r="D172" t="s">
         <v>63</v>
@@ -2996,7 +2996,7 @@
         <v>49</v>
       </c>
       <c r="C174">
-        <v>52.38</v>
+        <v>-52.38</v>
       </c>
       <c r="D174" t="s">
         <v>62</v>
@@ -3010,7 +3010,7 @@
         <v>37</v>
       </c>
       <c r="C175">
-        <v>994.0700000000001</v>
+        <v>-994.0700000000001</v>
       </c>
       <c r="D175" t="s">
         <v>61</v>
@@ -3024,7 +3024,7 @@
         <v>45</v>
       </c>
       <c r="C176">
-        <v>99.84</v>
+        <v>-99.84</v>
       </c>
       <c r="D176" t="s">
         <v>56</v>
@@ -3038,7 +3038,7 @@
         <v>44</v>
       </c>
       <c r="C177">
-        <v>49.62</v>
+        <v>-49.62</v>
       </c>
       <c r="D177" t="s">
         <v>57</v>
@@ -3052,7 +3052,7 @@
         <v>44</v>
       </c>
       <c r="C178">
-        <v>208.3</v>
+        <v>-208.3</v>
       </c>
       <c r="D178" t="s">
         <v>57</v>
@@ -3066,7 +3066,7 @@
         <v>37</v>
       </c>
       <c r="C179">
-        <v>186.95</v>
+        <v>-186.95</v>
       </c>
       <c r="D179" t="s">
         <v>61</v>
@@ -3094,7 +3094,7 @@
         <v>38</v>
       </c>
       <c r="C181">
-        <v>87.34999999999999</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="D181" t="s">
         <v>62</v>
@@ -3108,7 +3108,7 @@
         <v>44</v>
       </c>
       <c r="C182">
-        <v>263.09</v>
+        <v>-263.09</v>
       </c>
       <c r="D182" t="s">
         <v>57</v>
@@ -3122,7 +3122,7 @@
         <v>36</v>
       </c>
       <c r="C183">
-        <v>6.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D183" t="s">
         <v>60</v>
@@ -3136,7 +3136,7 @@
         <v>43</v>
       </c>
       <c r="C184">
-        <v>46.63</v>
+        <v>-46.63</v>
       </c>
       <c r="D184" t="s">
         <v>58</v>
@@ -3150,7 +3150,7 @@
         <v>52</v>
       </c>
       <c r="C185">
-        <v>308.29</v>
+        <v>-308.29</v>
       </c>
       <c r="D185" t="s">
         <v>63</v>
@@ -3164,7 +3164,7 @@
         <v>38</v>
       </c>
       <c r="C186">
-        <v>54.07</v>
+        <v>-54.07</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -3178,7 +3178,7 @@
         <v>54</v>
       </c>
       <c r="C187">
-        <v>89.62</v>
+        <v>-89.62</v>
       </c>
       <c r="D187" t="s">
         <v>58</v>
@@ -3206,7 +3206,7 @@
         <v>52</v>
       </c>
       <c r="C189">
-        <v>118.26</v>
+        <v>-118.26</v>
       </c>
       <c r="D189" t="s">
         <v>63</v>
@@ -3220,7 +3220,7 @@
         <v>32</v>
       </c>
       <c r="C190">
-        <v>46.63</v>
+        <v>-46.63</v>
       </c>
       <c r="D190" t="s">
         <v>56</v>
@@ -3234,7 +3234,7 @@
         <v>43</v>
       </c>
       <c r="C191">
-        <v>21.22</v>
+        <v>-21.22</v>
       </c>
       <c r="D191" t="s">
         <v>58</v>
@@ -3248,7 +3248,7 @@
         <v>52</v>
       </c>
       <c r="C192">
-        <v>96.34</v>
+        <v>-96.34</v>
       </c>
       <c r="D192" t="s">
         <v>63</v>
@@ -3262,7 +3262,7 @@
         <v>45</v>
       </c>
       <c r="C193">
-        <v>95.19</v>
+        <v>-95.19</v>
       </c>
       <c r="D193" t="s">
         <v>56</v>
@@ -3276,7 +3276,7 @@
         <v>46</v>
       </c>
       <c r="C194">
-        <v>29.26</v>
+        <v>-29.26</v>
       </c>
       <c r="D194" t="s">
         <v>56</v>
@@ -3304,7 +3304,7 @@
         <v>42</v>
       </c>
       <c r="C196">
-        <v>835.99</v>
+        <v>-835.99</v>
       </c>
       <c r="D196" t="s">
         <v>61</v>
@@ -3318,7 +3318,7 @@
         <v>36</v>
       </c>
       <c r="C197">
-        <v>2.26</v>
+        <v>-2.26</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
@@ -3332,7 +3332,7 @@
         <v>32</v>
       </c>
       <c r="C198">
-        <v>43.1</v>
+        <v>-43.1</v>
       </c>
       <c r="D198" t="s">
         <v>56</v>
@@ -3346,7 +3346,7 @@
         <v>32</v>
       </c>
       <c r="C199">
-        <v>43.49</v>
+        <v>-43.49</v>
       </c>
       <c r="D199" t="s">
         <v>56</v>
@@ -3360,7 +3360,7 @@
         <v>55</v>
       </c>
       <c r="C200">
-        <v>28.55</v>
+        <v>-28.55</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
@@ -3374,7 +3374,7 @@
         <v>36</v>
       </c>
       <c r="C201">
-        <v>43.79</v>
+        <v>-43.79</v>
       </c>
       <c r="D201" t="s">
         <v>60</v>
